--- a/website/examples/example_odk_admin_fingerprint_confirmation.xlsx
+++ b/website/examples/example_odk_admin_fingerprint_confirmation.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rb70530cc0a834d18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R3f36cbfbf65f4207"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R8c23e2018ab54d41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R8902e324e04f4dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R1bde603817784194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Re3f44053874a4ade"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -393,7 +393,7 @@
         <x:v>intro</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Select an Android authentication policy, then launch ResearchOS.</x:v>
+        <x:v>Select an Android authentication policy, then launch MethodMesh.</x:v>
       </x:c>
       <x:c r="D2" s="11"/>
       <x:c r="E2" s="11"/>
@@ -435,7 +435,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='admin_fingerprint_confirmation',input_authentication_method=${authentication_method})</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='admin_fingerprint_confirmation',input_authentication_method=${authentication_method})</x:v>
       </x:c>
       <x:c r="F4" s="11"/>
       <x:c r="G4" s="11"/>
@@ -447,10 +447,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D5" s="11"/>
       <x:c r="E5" s="11"/>
@@ -464,10 +464,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D6" s="11"/>
       <x:c r="E6" s="11"/>
@@ -740,7 +740,7 @@
         <x:v>2026072707</x:v>
       </x:c>
       <x:c r="D2" s="12" t="str">
-        <x:v>${researchos_status}</x:v>
+        <x:v>${methodmesh_status}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
